--- a/output/topology_excel/7727.xlsx
+++ b/output/topology_excel/7727.xlsx
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B23" t="n">
         <v>26</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B24" t="n">
         <v>27</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>559</v>
+        <v>509</v>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>451</v>
+        <v>373</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,19 +1092,19 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>657</v>
+        <v>290</v>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" t="n">
         <v>3</v>
       </c>
-      <c r="B31" t="n">
-        <v>12</v>
-      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>205</v>
+        <v>451</v>
       </c>
       <c r="F31" t="n">
         <v>23</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>808</v>
+        <v>559</v>
       </c>
       <c r="F32" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>509</v>
+        <v>657</v>
       </c>
       <c r="F33" t="n">
         <v>23</v>
@@ -1166,11 +1166,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" t="n">
         <v>4</v>
       </c>
-      <c r="B34" t="n">
-        <v>16</v>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>373</v>
+        <v>205</v>
       </c>
       <c r="F34" t="n">
         <v>23</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B35" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,19 +1202,19 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>186</v>
+        <v>808</v>
       </c>
       <c r="F35" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="n">
         <v>4</v>
       </c>
-      <c r="B36" t="n">
-        <v>23</v>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1224,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>144</v>
+        <v>580</v>
       </c>
       <c r="F36" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -1235,7 +1235,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>126</v>
+        <v>352</v>
       </c>
       <c r="F37" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="F38" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -1290,10 +1290,10 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>578</v>
+        <v>126</v>
       </c>
       <c r="F39" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -1301,7 +1301,7 @@
         <v>5</v>
       </c>
       <c r="B40" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>519</v>
+        <v>248</v>
       </c>
       <c r="F40" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="F41" t="n">
         <v>24</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="F42" t="n">
         <v>24</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B43" t="n">
         <v>11</v>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>368</v>
+        <v>244</v>
       </c>
       <c r="F43" t="n">
-        <v>24</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B44" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="F44" t="n">
-        <v>105</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>220</v>
+        <v>86</v>
       </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46">
@@ -1433,7 +1433,7 @@
         <v>7</v>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1053</v>
+        <v>160</v>
       </c>
       <c r="F46" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
@@ -1455,7 +1455,7 @@
         <v>7</v>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>663</v>
+        <v>48</v>
       </c>
       <c r="F47" t="n">
-        <v>289</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B48" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F48" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -1499,7 +1499,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,18 +1510,18 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>264</v>
+        <v>144</v>
       </c>
       <c r="F49" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="F50" t="n">
         <v>24</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>165</v>
+        <v>578</v>
       </c>
       <c r="F51" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B52" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>578</v>
+        <v>519</v>
       </c>
       <c r="F52" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>309</v>
+        <v>208</v>
       </c>
       <c r="F53" t="n">
         <v>24</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="F54" t="n">
         <v>24</v>
@@ -1631,7 +1631,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>150</v>
+        <v>368</v>
       </c>
       <c r="F55" t="n">
         <v>24</v>
@@ -1653,7 +1653,7 @@
         <v>11</v>
       </c>
       <c r="B56" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="F56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -1675,7 +1675,7 @@
         <v>12</v>
       </c>
       <c r="B57" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>352</v>
+        <v>1053</v>
       </c>
       <c r="F57" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58">
@@ -1697,7 +1697,7 @@
         <v>12</v>
       </c>
       <c r="B58" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,18 +1708,18 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>183</v>
+        <v>663</v>
       </c>
       <c r="F58" t="n">
-        <v>44</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B59" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>121</v>
+        <v>182</v>
       </c>
       <c r="F59" t="n">
         <v>24</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B60" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="F60" t="n">
         <v>24</v>
@@ -1774,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>208</v>
+        <v>121</v>
       </c>
       <c r="F61" t="n">
         <v>24</v>
@@ -1785,7 +1785,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="F62" t="n">
-        <v>82</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
@@ -1807,7 +1807,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,18 +1818,18 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>160</v>
+        <v>578</v>
       </c>
       <c r="F63" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B64" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,18 +1840,18 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>48</v>
+        <v>309</v>
       </c>
       <c r="F64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B65" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,18 +1862,18 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>261</v>
+        <v>150</v>
       </c>
       <c r="F65" t="n">
-        <v>109</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,18 +1884,18 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1906,18 +1906,18 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>601</v>
+        <v>309</v>
       </c>
       <c r="F67" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B68" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,18 +1928,18 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="F68" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B69" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,18 +1950,18 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>309</v>
+        <v>138</v>
       </c>
       <c r="F69" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B70" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1972,18 +1972,18 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>60</v>
+        <v>309</v>
       </c>
       <c r="F70" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B71" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1994,18 +1994,18 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="F71" t="n">
-        <v>171</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B72" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2016,18 +2016,18 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>138</v>
+        <v>290</v>
       </c>
       <c r="F72" t="n">
-        <v>24</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B73" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2038,15 +2038,15 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>249</v>
+        <v>138</v>
       </c>
       <c r="F73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B74" t="n">
         <v>25</v>
@@ -2060,10 +2060,10 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F74" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75">

--- a/output/topology_excel/7727.xlsx
+++ b/output/topology_excel/7727.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,42 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
         </is>
       </c>
     </row>
@@ -473,7 +503,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>316</v>
@@ -481,6 +511,12 @@
       <c r="F2" t="n">
         <v>88</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +539,12 @@
       <c r="F3" t="n">
         <v>23</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +567,12 @@
       <c r="F4" t="n">
         <v>23</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +595,12 @@
       <c r="F5" t="n">
         <v>23</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +623,12 @@
       <c r="F6" t="n">
         <v>24</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +651,12 @@
       <c r="F7" t="n">
         <v>42</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +679,12 @@
       <c r="F8" t="n">
         <v>29</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +707,12 @@
       <c r="F9" t="n">
         <v>24</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +735,12 @@
       <c r="F10" t="n">
         <v>24</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +763,12 @@
       <c r="F11" t="n">
         <v>24</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +791,12 @@
       <c r="F12" t="n">
         <v>24</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +819,12 @@
       <c r="F13" t="n">
         <v>23</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +847,12 @@
       <c r="F14" t="n">
         <v>24</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +875,12 @@
       <c r="F15" t="n">
         <v>23</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +903,12 @@
       <c r="F16" t="n">
         <v>23</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +931,12 @@
       <c r="F17" t="n">
         <v>14</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +959,12 @@
       <c r="F18" t="n">
         <v>23</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +987,12 @@
       <c r="F19" t="n">
         <v>19</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +1015,12 @@
       <c r="F20" t="n">
         <v>15</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +1043,12 @@
       <c r="F21" t="n">
         <v>45</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +1071,12 @@
       <c r="F22" t="n">
         <v>44</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1099,12 @@
       <c r="F23" t="n">
         <v>44</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1127,12 @@
       <c r="F24" t="n">
         <v>44</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1155,12 @@
       <c r="F25" t="n">
         <v>23</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1001,7 +1175,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>122</v>
@@ -1009,6 +1183,12 @@
       <c r="F26" t="n">
         <v>46</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1023,14 +1203,24 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>509</v>
+        <v>384</v>
       </c>
       <c r="F27" t="n">
         <v>23</v>
       </c>
+      <c r="G27" t="n">
+        <v>102</v>
+      </c>
+      <c r="H27" t="n">
+        <v>23</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1243,12 @@
       <c r="F28" t="n">
         <v>23</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1067,14 +1263,24 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>601</v>
+        <v>147</v>
       </c>
       <c r="F29" t="n">
         <v>19</v>
       </c>
+      <c r="G29" t="n">
+        <v>432</v>
+      </c>
+      <c r="H29" t="n">
+        <v>19</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1089,14 +1295,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>290</v>
+        <v>96</v>
       </c>
       <c r="F30" t="n">
-        <v>119</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G30" t="n">
+        <v>78</v>
+      </c>
+      <c r="H30" t="n">
+        <v>23</v>
+      </c>
+      <c r="I30" t="n">
+        <v>151</v>
+      </c>
+      <c r="J30" t="n">
+        <v>23</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1339,12 @@
       <c r="F31" t="n">
         <v>23</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1133,14 +1359,24 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>559</v>
+        <v>266</v>
       </c>
       <c r="F32" t="n">
         <v>44</v>
       </c>
+      <c r="G32" t="n">
+        <v>270</v>
+      </c>
+      <c r="H32" t="n">
+        <v>44</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1399,12 @@
       <c r="F33" t="n">
         <v>23</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1427,12 @@
       <c r="F34" t="n">
         <v>23</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1199,14 +1447,28 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>808</v>
+        <v>45</v>
       </c>
       <c r="F35" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>334</v>
+      </c>
+      <c r="H35" t="n">
+        <v>23</v>
+      </c>
+      <c r="I35" t="n">
+        <v>432</v>
+      </c>
+      <c r="J35" t="n">
+        <v>23</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1491,12 @@
       <c r="F36" t="n">
         <v>23</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1519,12 @@
       <c r="F37" t="n">
         <v>23</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1547,12 @@
       <c r="F38" t="n">
         <v>44</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1293,8 +1573,14 @@
         <v>126</v>
       </c>
       <c r="F39" t="n">
-        <v>44</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1603,12 @@
       <c r="F40" t="n">
         <v>44</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1631,12 @@
       <c r="F41" t="n">
         <v>24</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1659,12 @@
       <c r="F42" t="n">
         <v>24</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1375,14 +1679,24 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="F43" t="n">
-        <v>105</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G43" t="n">
+        <v>220</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1719,12 @@
       <c r="F44" t="n">
         <v>24</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1425,8 +1745,14 @@
         <v>86</v>
       </c>
       <c r="F45" t="n">
-        <v>82</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1775,12 @@
       <c r="F46" t="n">
         <v>24</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1803,12 @@
       <c r="F47" t="n">
         <v>25</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1491,8 +1829,14 @@
         <v>186</v>
       </c>
       <c r="F48" t="n">
-        <v>44</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1513,8 +1857,14 @@
         <v>144</v>
       </c>
       <c r="F49" t="n">
-        <v>44</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1887,12 @@
       <c r="F50" t="n">
         <v>24</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1915,12 @@
       <c r="F51" t="n">
         <v>45</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1943,12 @@
       <c r="F52" t="n">
         <v>45</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1971,12 @@
       <c r="F53" t="n">
         <v>24</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1999,12 @@
       <c r="F54" t="n">
         <v>24</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +2027,12 @@
       <c r="F55" t="n">
         <v>24</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +2055,12 @@
       <c r="F56" t="n">
         <v>24</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +2083,12 @@
       <c r="F57" t="n">
         <v>29</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1705,13 +2103,31 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>663</v>
+        <v>247</v>
       </c>
       <c r="F58" t="n">
-        <v>289</v>
+        <v>42</v>
+      </c>
+      <c r="G58" t="n">
+        <v>166</v>
+      </c>
+      <c r="H58" t="n">
+        <v>42</v>
+      </c>
+      <c r="I58" t="n">
+        <v>371</v>
+      </c>
+      <c r="J58" t="n">
+        <v>42</v>
+      </c>
+      <c r="K58" t="n">
+        <v>247</v>
+      </c>
+      <c r="L58" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="59">
@@ -1735,6 +2151,12 @@
       <c r="F59" t="n">
         <v>24</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +2179,12 @@
       <c r="F60" t="n">
         <v>24</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +2207,12 @@
       <c r="F61" t="n">
         <v>24</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +2235,12 @@
       <c r="F62" t="n">
         <v>24</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1823,6 +2263,12 @@
       <c r="F63" t="n">
         <v>44</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +2291,12 @@
       <c r="F64" t="n">
         <v>24</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2319,12 @@
       <c r="F65" t="n">
         <v>24</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1889,6 +2347,12 @@
       <c r="F66" t="n">
         <v>23</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2375,12 @@
       <c r="F67" t="n">
         <v>24</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1925,14 +2395,24 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>261</v>
+        <v>95</v>
       </c>
       <c r="F68" t="n">
-        <v>109</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G68" t="n">
+        <v>247</v>
+      </c>
+      <c r="H68" t="n">
+        <v>14</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2435,12 @@
       <c r="F69" t="n">
         <v>15</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2463,12 @@
       <c r="F70" t="n">
         <v>24</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1999,6 +2491,12 @@
       <c r="F71" t="n">
         <v>44</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2013,14 +2511,24 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>290</v>
+        <v>148</v>
       </c>
       <c r="F72" t="n">
-        <v>171</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="G72" t="n">
+        <v>246</v>
+      </c>
+      <c r="H72" t="n">
+        <v>23</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2043,6 +2551,12 @@
       <c r="F73" t="n">
         <v>24</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2065,6 +2579,12 @@
       <c r="F74" t="n">
         <v>23</v>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2087,6 +2607,12 @@
       <c r="F75" t="n">
         <v>23</v>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
